--- a/assets/FIFA_Pitch_Performance_Standards.xlsx
+++ b/assets/FIFA_Pitch_Performance_Standards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dillonmccallum/Documents/GitHub/labosport-app/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8274AC1C-7FB0-FC41-9778-CBE148E17006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A3DDDA-8D3B-0D4E-981C-419A88B392EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="440" yWindow="500" windowWidth="35400" windowHeight="21900" xr2:uid="{55D85911-D159-6C4A-A7AD-576153E59277}"/>
   </bookViews>
@@ -372,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -385,9 +385,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -395,6 +392,21 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,63 +788,63 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="63" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="14"/>
+      <c r="G2" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="63" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="15" t="s">
         <v>18</v>
       </c>
     </row>
@@ -843,241 +855,241 @@
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="63" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="63" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
+    <row r="6" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A6" s="5"/>
       <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
+      <c r="A8" s="5"/>
       <c r="B8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="21" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="21" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="84" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:7" ht="63" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="15" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="84" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
+    <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.2">
+      <c r="A12" s="5"/>
       <c r="B12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:7" ht="21" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="15" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="84" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
+    <row r="14" spans="1:7" ht="63" x14ac:dyDescent="0.2">
+      <c r="A14" s="5"/>
       <c r="B14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="15" t="s">
         <v>84</v>
       </c>
     </row>

--- a/assets/FIFA_Pitch_Performance_Standards.xlsx
+++ b/assets/FIFA_Pitch_Performance_Standards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dillonmccallum/Documents/GitHub/labosport-app/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A3DDDA-8D3B-0D4E-981C-419A88B392EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E1373E-8ACD-9248-A8CC-68E1B5D8B3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="440" yWindow="500" windowWidth="35400" windowHeight="21900" xr2:uid="{55D85911-D159-6C4A-A7AD-576153E59277}"/>
   </bookViews>
@@ -276,9 +276,6 @@
     <t>15.0-19.9 %</t>
   </si>
   <si>
-    <t>10.0-24.9 %</t>
-  </si>
-  <si>
     <t>25.0-30.0%</t>
   </si>
   <si>
@@ -295,6 +292,9 @@
   </si>
   <si>
     <t>15.0-20.0 %</t>
+  </si>
+  <si>
+    <t>20.0-24.9 %</t>
   </si>
 </sst>
 </file>
@@ -1066,10 +1066,10 @@
         <v>77</v>
       </c>
       <c r="F13" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>78</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="63" x14ac:dyDescent="0.2">
@@ -1078,19 +1078,19 @@
         <v>21</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="E14" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="G14" s="15" t="s">
         <v>83</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
